--- a/Excel/StartConfig/BanHao/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/BanHao/StartZoneConfig@s.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25831"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\StartConfig\BanHao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4B548D-C810-432C-8481-98785DF8663A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B50D21-3800-4C8B-9917-36EF5A411590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="675" windowWidth="27810" windowHeight="12315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2925" yWindow="900" windowWidth="24990" windowHeight="13410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Id</t>
   </si>
@@ -71,6 +71,14 @@
   </si>
   <si>
     <t>物理区</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeiJing203(robot)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -449,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:G7"/>
+  <dimension ref="C3:G8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -536,6 +544,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C8" s="2">
+        <v>203</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4">
+        <v>203</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/BanHao/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/BanHao/StartZoneConfig@s.xlsx
@@ -91,31 +91,31 @@
     <t>mongodb://localhost:27017/</t>
   </si>
   <si>
-    <t>WJBH1</t>
-  </si>
-  <si>
-    <t>WJBH2</t>
+    <t>WJBanHao1</t>
+  </si>
+  <si>
+    <t>WJBanHao2</t>
   </si>
   <si>
     <t>封测区</t>
   </si>
   <si>
-    <t>WJBH3</t>
-  </si>
-  <si>
-    <t>WJBH4</t>
-  </si>
-  <si>
-    <t>WJBH5</t>
-  </si>
-  <si>
-    <t>WJBH202(center)</t>
+    <t>WJBanHao3</t>
+  </si>
+  <si>
+    <t>WJBanHao4</t>
+  </si>
+  <si>
+    <t>WJBanHao201</t>
+  </si>
+  <si>
+    <t>WJBanHao202(center)</t>
   </si>
   <si>
     <t>#中心服</t>
   </si>
   <si>
-    <t>WJBH203(robot)</t>
+    <t>WJBanHao203(robot)</t>
   </si>
   <si>
     <t>#机器人</t>
@@ -297,12 +297,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -762,7 +762,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -776,6 +776,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1140,7 +1143,7 @@
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6">
+    <row r="3" spans="3:7">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1154,7 +1157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:6">
+    <row r="4" spans="3:7">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -1168,7 +1171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="3:6">
+    <row r="5" spans="3:7">
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1182,7 +1185,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:6">
+    <row r="6" s="1" customFormat="1" spans="3:7">
       <c r="C6" s="5">
         <v>1</v>
       </c>
@@ -1249,13 +1252,13 @@
     </row>
     <row r="10" spans="3:7">
       <c r="C10" s="3">
-        <v>5</v>
+        <v>201</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="5">
-        <v>5</v>
+        <v>201</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>15</v>
@@ -1274,7 +1277,7 @@
       <c r="E11" s="5">
         <v>202</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="2" t="s">

--- a/Excel/StartConfig/BanHao/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/BanHao/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
   <si>
     <t>Id</t>
   </si>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t>WJBanHao4</t>
-  </si>
-  <si>
-    <t>WJBanHao201</t>
   </si>
   <si>
     <t>WJBanHao202(center)</t>
@@ -1128,7 +1125,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:G12"/>
+  <dimension ref="C3:G11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1252,53 +1249,36 @@
     </row>
     <row r="10" spans="3:7">
       <c r="C10" s="3">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="5">
-        <v>201</v>
-      </c>
-      <c r="F10" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="3:7">
       <c r="C11" s="3">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="5">
-        <v>202</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>16</v>
+        <v>203</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="3:7">
-      <c r="C12" s="3">
-        <v>203</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="5">
-        <v>203</v>
-      </c>
-      <c r="F12" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/BanHao/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/BanHao/StartZoneConfig@s.xlsx
@@ -91,28 +91,28 @@
     <t>mongodb://localhost:27017/</t>
   </si>
   <si>
-    <t>WJBanHao1</t>
-  </si>
-  <si>
-    <t>WJBanHao2</t>
+    <t>WJBH1</t>
+  </si>
+  <si>
+    <t>WJBH2</t>
   </si>
   <si>
     <t>封测区</t>
   </si>
   <si>
-    <t>WJBanHao3</t>
-  </si>
-  <si>
-    <t>WJBanHao4</t>
-  </si>
-  <si>
-    <t>WJBanHao202(center)</t>
+    <t>WJBH3</t>
+  </si>
+  <si>
+    <t>WJBH4</t>
+  </si>
+  <si>
+    <t>WJBH202(center)</t>
   </si>
   <si>
     <t>#中心服</t>
   </si>
   <si>
-    <t>WJBanHao203(robot)</t>
+    <t>WJBH203(robot)</t>
   </si>
   <si>
     <t>#机器人</t>
